--- a/artfynd/A 38585-2025 artfynd.xlsx
+++ b/artfynd/A 38585-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126836335</v>
       </c>
       <c r="B2" t="n">
-        <v>56613</v>
+        <v>56617</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126836410</v>
+        <v>126836535</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>78685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>681701</v>
+        <v>681550</v>
       </c>
       <c r="R3" t="n">
-        <v>7087141</v>
+        <v>7087261</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126836535</v>
+        <v>126836411</v>
       </c>
       <c r="B4" t="n">
-        <v>78681</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>681550</v>
+        <v>681668</v>
       </c>
       <c r="R4" t="n">
-        <v>7087261</v>
+        <v>7087157</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126828321</v>
+        <v>126836410</v>
       </c>
       <c r="B5" t="n">
-        <v>57817</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,46 +989,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Röjdtjärnbäcken, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>681441</v>
+        <v>681701</v>
       </c>
       <c r="R5" t="n">
-        <v>7087203</v>
+        <v>7087141</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,19 +1046,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,12 +1063,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1101,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126837195</v>
+        <v>126828321</v>
       </c>
       <c r="B6" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,16 +1112,24 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>681474</v>
+        <v>681441</v>
       </c>
       <c r="R6" t="n">
-        <v>7087200</v>
+        <v>7087203</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,9 +1159,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,12 +1186,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1206,10 +1202,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126836411</v>
+        <v>126837195</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>57821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,34 +1213,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>681668</v>
+        <v>681474</v>
       </c>
       <c r="R7" t="n">
-        <v>7087157</v>
+        <v>7087200</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,12 +1291,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1310,7 +1310,7 @@
         <v>126836412</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>126836409</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>126836415</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>126836417</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>126836416</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>126836296</v>
       </c>
       <c r="B13" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126836429</v>
+        <v>126836430</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>681552</v>
+        <v>681561</v>
       </c>
       <c r="R14" t="n">
-        <v>7087250</v>
+        <v>7087229</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126836430</v>
+        <v>126836413</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>681561</v>
+        <v>681654</v>
       </c>
       <c r="R15" t="n">
-        <v>7087229</v>
+        <v>7087171</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2115,10 +2115,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126836413</v>
+        <v>126836429</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>681654</v>
+        <v>681552</v>
       </c>
       <c r="R16" t="n">
-        <v>7087171</v>
+        <v>7087250</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,7 +2219,7 @@
         <v>126836418</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>126836419</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>126836414</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>126836428</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>126836235</v>
       </c>
       <c r="B21" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>126836420</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>126836298</v>
       </c>
       <c r="B23" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 38585-2025 artfynd.xlsx
+++ b/artfynd/A 38585-2025 artfynd.xlsx
@@ -1913,7 +1913,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126836430</v>
+        <v>126836429</v>
       </c>
       <c r="B14" t="n">
         <v>79018</v>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>681561</v>
+        <v>681552</v>
       </c>
       <c r="R14" t="n">
-        <v>7087229</v>
+        <v>7087250</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126836413</v>
+        <v>126836430</v>
       </c>
       <c r="B15" t="n">
         <v>79018</v>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>681654</v>
+        <v>681561</v>
       </c>
       <c r="R15" t="n">
-        <v>7087171</v>
+        <v>7087229</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2115,7 +2115,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126836429</v>
+        <v>126836413</v>
       </c>
       <c r="B16" t="n">
         <v>79018</v>
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>681552</v>
+        <v>681654</v>
       </c>
       <c r="R16" t="n">
-        <v>7087250</v>
+        <v>7087171</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 38585-2025 artfynd.xlsx
+++ b/artfynd/A 38585-2025 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126836535</v>
+        <v>126828321</v>
       </c>
       <c r="B3" t="n">
-        <v>78685</v>
+        <v>57821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,34 +787,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>681550</v>
+        <v>681441</v>
       </c>
       <c r="R3" t="n">
-        <v>7087261</v>
+        <v>7087203</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -844,9 +856,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,12 +883,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126836411</v>
+        <v>126837195</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,34 +910,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>681668</v>
+        <v>681474</v>
       </c>
       <c r="R4" t="n">
-        <v>7087157</v>
+        <v>7087200</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +988,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126836410</v>
+        <v>126836535</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>681701</v>
+        <v>681550</v>
       </c>
       <c r="R5" t="n">
-        <v>7087141</v>
+        <v>7087261</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126828321</v>
+        <v>126836411</v>
       </c>
       <c r="B6" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,46 +1116,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Röjdtjärnbäcken, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>681441</v>
+        <v>681668</v>
       </c>
       <c r="R6" t="n">
-        <v>7087203</v>
+        <v>7087157</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,19 +1173,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1186,12 +1190,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1202,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126837195</v>
+        <v>126836410</v>
       </c>
       <c r="B7" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1213,38 +1217,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>681474</v>
+        <v>681701</v>
       </c>
       <c r="R7" t="n">
-        <v>7087200</v>
+        <v>7087141</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,12 +1291,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">

--- a/artfynd/A 38585-2025 artfynd.xlsx
+++ b/artfynd/A 38585-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2928,6 +2928,312 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129524843</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lämkullen, Lämkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>681651</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7087106</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129524855</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lämkullen, Lämkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>681686</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7087090</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Flera färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129524804</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>681607</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7087176</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38585-2025 artfynd.xlsx
+++ b/artfynd/A 38585-2025 artfynd.xlsx
@@ -2934,7 +2934,7 @@
         <v>129524843</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>129524855</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>129524804</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 38585-2025 artfynd.xlsx
+++ b/artfynd/A 38585-2025 artfynd.xlsx
@@ -2934,7 +2934,7 @@
         <v>129524843</v>
       </c>
       <c r="B24" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>129524855</v>
       </c>
       <c r="B25" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>129524804</v>
       </c>
       <c r="B26" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 38585-2025 artfynd.xlsx
+++ b/artfynd/A 38585-2025 artfynd.xlsx
@@ -2934,7 +2934,7 @@
         <v>129524843</v>
       </c>
       <c r="B24" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>129524855</v>
       </c>
       <c r="B25" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>129524804</v>
       </c>
       <c r="B26" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 38585-2025 artfynd.xlsx
+++ b/artfynd/A 38585-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126836335</v>
       </c>
       <c r="B2" t="n">
-        <v>56617</v>
+        <v>56613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126828321</v>
       </c>
       <c r="B3" t="n">
-        <v>57821</v>
+        <v>57817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>126837195</v>
       </c>
       <c r="B4" t="n">
-        <v>57821</v>
+        <v>57817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>126836535</v>
       </c>
       <c r="B5" t="n">
-        <v>78685</v>
+        <v>78678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>126836411</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>126836410</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>126836412</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>126836409</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>126836415</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>126836417</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>126836416</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>126836296</v>
       </c>
       <c r="B13" t="n">
-        <v>78777</v>
+        <v>78770</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>126836429</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>126836430</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>126836413</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>126836418</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>126836419</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>126836414</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>126836428</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>126836235</v>
       </c>
       <c r="B21" t="n">
-        <v>57821</v>
+        <v>57817</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>126836420</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>126836298</v>
       </c>
       <c r="B23" t="n">
-        <v>78777</v>
+        <v>78770</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 38585-2025 artfynd.xlsx
+++ b/artfynd/A 38585-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126836335</v>
+        <v>126836535</v>
       </c>
       <c r="B2" t="n">
-        <v>56617</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208260</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>681761</v>
+        <v>681550</v>
       </c>
       <c r="R2" t="n">
-        <v>7087083</v>
+        <v>7087261</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,57 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126828321</v>
+        <v>126836409</v>
       </c>
       <c r="B3" t="n">
-        <v>57821</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Röjdtjärnbäcken, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>681441</v>
+        <v>681719</v>
       </c>
       <c r="R3" t="n">
-        <v>7087203</v>
+        <v>7087119</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,19 +844,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -899,49 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126837195</v>
+        <v>126836410</v>
       </c>
       <c r="B4" t="n">
-        <v>57821</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>681474</v>
+        <v>681701</v>
       </c>
       <c r="R4" t="n">
-        <v>7087200</v>
+        <v>7087141</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1004,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126836535</v>
+        <v>126836411</v>
       </c>
       <c r="B5" t="n">
-        <v>78685</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>681550</v>
+        <v>681668</v>
       </c>
       <c r="R5" t="n">
-        <v>7087261</v>
+        <v>7087157</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,14 +1079,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126836411</v>
+        <v>126836412</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1140,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>681668</v>
+        <v>681654</v>
       </c>
       <c r="R6" t="n">
-        <v>7087157</v>
+        <v>7087160</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,14 +1180,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126836410</v>
+        <v>126836413</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1241,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>681701</v>
+        <v>681654</v>
       </c>
       <c r="R7" t="n">
-        <v>7087141</v>
+        <v>7087171</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,14 +1281,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126836412</v>
+        <v>126836414</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1342,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>681654</v>
+        <v>681657</v>
       </c>
       <c r="R8" t="n">
-        <v>7087160</v>
+        <v>7087178</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,14 +1382,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126836409</v>
+        <v>126836415</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1443,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>681719</v>
+        <v>681651</v>
       </c>
       <c r="R9" t="n">
-        <v>7087119</v>
+        <v>7087182</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,14 +1483,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126836415</v>
+        <v>126836416</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1544,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>681651</v>
+        <v>681635</v>
       </c>
       <c r="R10" t="n">
-        <v>7087182</v>
+        <v>7087184</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,11 +1587,11 @@
         <v>126836417</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1711,14 +1685,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126836416</v>
+        <v>126836418</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1746,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>681635</v>
+        <v>681609</v>
       </c>
       <c r="R12" t="n">
-        <v>7087184</v>
+        <v>7087237</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,32 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126836296</v>
+        <v>126836419</v>
       </c>
       <c r="B13" t="n">
-        <v>78777</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>681762</v>
+        <v>681608</v>
       </c>
       <c r="R13" t="n">
-        <v>7087081</v>
+        <v>7087243</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,14 +1887,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126836429</v>
+        <v>126836420</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1948,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>681552</v>
+        <v>681604</v>
       </c>
       <c r="R14" t="n">
-        <v>7087250</v>
+        <v>7087246</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,14 +1988,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126836430</v>
+        <v>126836427</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2049,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>681561</v>
+        <v>681540</v>
       </c>
       <c r="R15" t="n">
-        <v>7087229</v>
+        <v>7087272</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2115,14 +2089,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126836413</v>
+        <v>126836428</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2150,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>681654</v>
+        <v>681547</v>
       </c>
       <c r="R16" t="n">
-        <v>7087171</v>
+        <v>7087252</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2216,14 +2190,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126836418</v>
+        <v>126836429</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2251,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>681609</v>
+        <v>681552</v>
       </c>
       <c r="R17" t="n">
-        <v>7087237</v>
+        <v>7087250</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,14 +2291,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126836419</v>
+        <v>126836430</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2352,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>681608</v>
+        <v>681561</v>
       </c>
       <c r="R18" t="n">
-        <v>7087243</v>
+        <v>7087229</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,14 +2392,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126836414</v>
+        <v>126836431</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2453,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>681657</v>
+        <v>681443</v>
       </c>
       <c r="R19" t="n">
-        <v>7087178</v>
+        <v>7087186</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2519,10 +2493,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126836428</v>
+        <v>129511110</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,34 +2504,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>681547</v>
+        <v>681532</v>
       </c>
       <c r="R20" t="n">
-        <v>7087252</v>
+        <v>7087283</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2584,12 +2558,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flera färska ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2604,26 +2583,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Herman Niva</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126836235</v>
+        <v>129511204</v>
       </c>
       <c r="B21" t="n">
-        <v>57821</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2631,42 +2606,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>681657</v>
+        <v>681531</v>
       </c>
       <c r="R21" t="n">
-        <v>7087178</v>
+        <v>7087270</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2693,12 +2660,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2713,26 +2685,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Herman Niva</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126836420</v>
+        <v>129511214</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2740,34 +2708,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>681604</v>
+        <v>681536</v>
       </c>
       <c r="R22" t="n">
-        <v>7087246</v>
+        <v>7087266</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2794,12 +2762,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Flera färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2814,26 +2787,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Herman Niva</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126836298</v>
+        <v>129524783</v>
       </c>
       <c r="B23" t="n">
-        <v>78777</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2841,34 +2810,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>681550</v>
+        <v>681534</v>
       </c>
       <c r="R23" t="n">
-        <v>7087262</v>
+        <v>7087259</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2895,12 +2864,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2915,26 +2889,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Herman Niva</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129524843</v>
+        <v>129524804</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2962,14 +2932,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lämkullen, Lämkullen, Ång</t>
+          <t>Lämkullmyran, Lämkullmyran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>681651</v>
+        <v>681607</v>
       </c>
       <c r="R24" t="n">
-        <v>7087106</v>
+        <v>7087176</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3033,10 +3003,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129524855</v>
+        <v>129524843</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3068,10 +3038,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>681686</v>
+        <v>681651</v>
       </c>
       <c r="R25" t="n">
-        <v>7087090</v>
+        <v>7087106</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,7 +3078,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Flera färska ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3135,10 +3105,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129524804</v>
+        <v>129524855</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3166,14 +3136,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lämkullmyran, Lämkullmyran, Ång</t>
+          <t>Lämkullen, Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>681607</v>
+        <v>681686</v>
       </c>
       <c r="R26" t="n">
-        <v>7087176</v>
+        <v>7087090</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3210,7 +3180,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Flera färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3234,6 +3204,747 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126828321</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Röjdtjärnbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>681441</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7087203</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Malin Löfgren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Malin Löfgren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126836235</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>681657</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7087178</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126837195</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>681474</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7087200</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126836335</v>
+      </c>
+      <c r="B30" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>681761</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7087083</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126836296</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>681762</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7087081</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126836297</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>681585</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7087270</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126836298</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>681550</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7087262</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38585-2025 artfynd.xlsx
+++ b/artfynd/A 38585-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836535</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836409</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836410</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836411</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836412</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836413</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836414</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836415</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836416</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836417</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836418</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836419</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836420</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836427</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836428</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836429</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836430</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836431</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2592,6 +2687,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129511110</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2694,6 +2794,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129511204</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2796,6 +2901,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129511214</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2898,6 +3008,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524783</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3000,6 +3115,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524804</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3102,6 +3222,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524843</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3204,6 +3329,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524855</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3327,6 +3457,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126828321</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3436,6 +3571,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836235</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3541,6 +3681,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837195</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3642,6 +3787,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836335</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3743,6 +3893,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836296</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3844,6 +3999,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836297</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3945,8 +4105,47 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836298</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>